--- a/gold_scoring_config.xlsx
+++ b/gold_scoring_config.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>SIMULATED</t>
+          <t>FRED_CALC</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -711,7 +711,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>SIMULATED</t>
+          <t>FRED_CALC</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
@@ -855,7 +855,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SIMULATED</t>
+          <t>FRED</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>SIMULATED</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>vol pts</t>
+          <t>index</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>SIMULATED</t>
+          <t>CME_XLS</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>SIMULATED</t>
+          <t>FRED_CALC</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>SIMULATED</t>
+          <t>FRED_CALC</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>SIMULATED</t>
+          <t>FRED_CALC</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>SIMULATED</t>
+          <t>FRED_CALC</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>SIMULATED</t>
+          <t>YF_CALC</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">

--- a/gold_scoring_config.xlsx
+++ b/gold_scoring_config.xlsx
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>

--- a/gold_scoring_config.xlsx
+++ b/gold_scoring_config.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
